--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DDV_HRM-2031-0252/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DDV_HRM-2031-0252/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.55258</v>
+        <v>16.68722</v>
       </c>
       <c r="D2" t="n">
-        <v>16.72433</v>
+        <v>16.55907</v>
       </c>
       <c r="E2" t="n">
-        <v>16.62755</v>
+        <v>16.6419</v>
       </c>
       <c r="F2" t="n">
-        <v>43.06696</v>
+        <v>42.70158</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05087</v>
+        <v>0.04991</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81812</v>
+        <v>1.77523</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.83789</v>
+        <v>16.66377</v>
       </c>
       <c r="D3" t="n">
-        <v>16.74785</v>
+        <v>16.50906</v>
       </c>
       <c r="E3" t="n">
-        <v>16.46291</v>
+        <v>16.51433</v>
       </c>
       <c r="F3" t="n">
-        <v>42.49192</v>
+        <v>42.8918</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05029</v>
+        <v>0.05082</v>
       </c>
       <c r="H3" t="n">
-        <v>1.77999</v>
+        <v>1.81053</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.31347</v>
+        <v>16.58912</v>
       </c>
       <c r="D4" t="n">
-        <v>16.26873</v>
+        <v>16.07191</v>
       </c>
       <c r="E4" t="n">
-        <v>16.75931</v>
+        <v>16.27852</v>
       </c>
       <c r="F4" t="n">
-        <v>43.40664</v>
+        <v>42.08926</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05136</v>
+        <v>0.05058</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80907</v>
+        <v>1.81277</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.89767</v>
+        <v>16.45628</v>
       </c>
       <c r="D6" t="n">
-        <v>15.93042</v>
+        <v>16.0489</v>
       </c>
       <c r="E6" t="n">
-        <v>16.53874</v>
+        <v>16.31724</v>
       </c>
       <c r="F6" t="n">
-        <v>21.99986</v>
+        <v>21.50308</v>
       </c>
       <c r="G6" t="n">
-        <v>33.66823</v>
+        <v>34.15331</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.56141</v>
+        <v>16.88111</v>
       </c>
       <c r="D7" t="n">
-        <v>15.85035</v>
+        <v>15.67017</v>
       </c>
       <c r="E7" t="n">
-        <v>16.38936</v>
+        <v>16.31758</v>
       </c>
       <c r="F7" t="n">
-        <v>21.75587</v>
+        <v>22.05966</v>
       </c>
       <c r="G7" t="n">
-        <v>34.74602</v>
+        <v>33.97216</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.49359</v>
+        <v>16.45669</v>
       </c>
       <c r="D8" t="n">
-        <v>15.66162</v>
+        <v>15.64355</v>
       </c>
       <c r="E8" t="n">
-        <v>16.53279</v>
+        <v>16.13417</v>
       </c>
       <c r="F8" t="n">
-        <v>21.67131</v>
+        <v>21.87083</v>
       </c>
       <c r="G8" t="n">
-        <v>34.37023</v>
+        <v>33.89578</v>
       </c>
     </row>
   </sheetData>
